--- a/vystupy/Dachbereich_Aussentank_soupis.xlsx
+++ b/vystupy/Dachbereich_Aussentank_soupis.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Párováno k nejbližšímu popisku 'P ≈ … W' (typicky 750 mm pod názvem; vzdálenost uvedena pro kontrolu). U '3x …' NENÍ ověřeno, zda výkon platí na kus, nebo celkem.</t>
+          <t>Párováno k nejbližšímu popisku 'P ≈ … W'. POTVRZENO (uživatel, 2026-10-06): výkon v popisku platí na 1 kus; u '3x …' je celkový výkon = počet × výkon. Viz sloupec 'Výkon celkem W'.</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Výkon W (nejbližší popisek P≈)</t>
+          <t>Výkon W na 1 kus (potvrzeno uživatelem)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -653,6 +653,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hladina</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Výkon celkem W (počet × výkon/ks)</t>
         </is>
       </c>
     </row>
